--- a/Users_Permissions.xlsx
+++ b/Users_Permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DominikDannenbauer\Documents\GitHub\project-dachau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CFA067-B26B-4260-97E5-0801EEE62FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB983B12-FA78-4832-9846-9C897EBA986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="273">
   <si>
     <t>Action</t>
   </si>
@@ -3067,8 +3067,8 @@
       <c r="E30" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="12" t="b">
-        <v>1</v>
+      <c r="F30" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="G30" s="12" t="b">
         <v>1</v>
@@ -3430,8 +3430,8 @@
       <c r="F38" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G38" s="12" t="b">
-        <v>1</v>
+      <c r="G38" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="H38" s="12" t="b">
         <v>1</v>

--- a/Users_Permissions.xlsx
+++ b/Users_Permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DominikDannenbauer\Documents\GitHub\project-dachau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB983B12-FA78-4832-9846-9C897EBA986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8229339B-6FF0-4E00-90E8-A006A1F23F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="273">
   <si>
     <t>Action</t>
   </si>
@@ -3070,8 +3070,8 @@
       <c r="F30" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="G30" s="12" t="b">
-        <v>1</v>
+      <c r="G30" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="H30" s="12" t="b">
         <v>1</v>

--- a/Users_Permissions.xlsx
+++ b/Users_Permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DominikDannenbauer\Documents\GitHub\project-dachau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8229339B-6FF0-4E00-90E8-A006A1F23F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFCABC1-C513-4A3B-9D92-C23B0350E23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3071,7 +3071,7 @@
         <v>271</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>271</v>
+        <v>40</v>
       </c>
       <c r="H30" s="12" t="b">
         <v>1</v>

--- a/Users_Permissions.xlsx
+++ b/Users_Permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DominikDannenbauer\Documents\GitHub\project-dachau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFCABC1-C513-4A3B-9D92-C23B0350E23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EAEA61-4E69-4F5B-AB0D-A9B2D9339115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Aktions-Glossar" sheetId="3" r:id="rId3"/>
     <sheet name="Legende" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="277">
   <si>
     <t>Action</t>
   </si>
@@ -855,6 +855,18 @@
   </si>
   <si>
     <t>DELETE</t>
+  </si>
+  <si>
+    <t>roland.mueller@lager.local</t>
+  </si>
+  <si>
+    <t>Roland Müller</t>
+  </si>
+  <si>
+    <t>Thomas Dietl</t>
+  </si>
+  <si>
+    <t>thomas.dietl@lager.local</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1111,10 +1123,12 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1706,7 +1720,7 @@
       <c r="B11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="26" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="19" t="s">
@@ -1729,10 +1743,14 @@
       <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>273</v>
+      </c>
       <c r="D12" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E12" s="4" t="b">
         <v>0</v>
@@ -1747,10 +1765,14 @@
       <c r="A13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>276</v>
+      </c>
       <c r="D13" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E13" s="4" t="b">
         <v>0</v>
@@ -1776,6 +1798,9 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C11" r:id="rId3" xr:uid="{CFF2D19F-E098-4C22-BC52-593DE09D4C64}"/>
+    <hyperlink ref="C12" r:id="rId4" xr:uid="{9EB08C06-4A05-4CB2-97D5-C8FE6CAF41A1}"/>
+    <hyperlink ref="C13" r:id="rId5" xr:uid="{D7BA793F-954A-405D-8FAE-D2538F88892A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1783,7 +1808,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" style="8" customWidth="1"/>
@@ -1793,10 +1818,11 @@
     <col min="5" max="5" width="12.6328125" style="8" customWidth="1"/>
     <col min="6" max="13" width="15" style="8" customWidth="1"/>
     <col min="14" max="14" width="21.54296875" style="8" customWidth="1"/>
-    <col min="15" max="15" width="30" style="8" customWidth="1"/>
+    <col min="15" max="16" width="25.81640625" style="21" customWidth="1"/>
+    <col min="17" max="17" width="30" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>45</v>
       </c>
@@ -1840,29 +1866,37 @@
         <v>42</v>
       </c>
       <c r="O1" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q1" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>51</v>
       </c>
@@ -1905,9 +1939,15 @@
       <c r="N3" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O3" s="13"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O3" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>51</v>
       </c>
@@ -1950,9 +1990,15 @@
       <c r="N4" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O4" s="13"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O4" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>51</v>
       </c>
@@ -1995,9 +2041,15 @@
       <c r="N5" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O5" s="13"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>51</v>
       </c>
@@ -2040,9 +2092,15 @@
       <c r="N6" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O6" s="13"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O6" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>51</v>
       </c>
@@ -2085,9 +2143,15 @@
       <c r="N7" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O7" s="13"/>
-    </row>
-    <row r="8" spans="1:15" ht="25" x14ac:dyDescent="0.35">
+      <c r="O7" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13"/>
+    </row>
+    <row r="8" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>51</v>
       </c>
@@ -2130,9 +2194,15 @@
       <c r="N8" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O8" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>51</v>
       </c>
@@ -2175,9 +2245,15 @@
       <c r="N9" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O9" s="13"/>
-    </row>
-    <row r="10" spans="1:15" ht="25" x14ac:dyDescent="0.35">
+      <c r="O9" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13"/>
+    </row>
+    <row r="10" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>51</v>
       </c>
@@ -2220,9 +2296,15 @@
       <c r="N10" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O10" s="13"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O10" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>51</v>
       </c>
@@ -2265,9 +2347,15 @@
       <c r="N11" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O11" s="13"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O11" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>51</v>
       </c>
@@ -2310,9 +2398,15 @@
       <c r="N12" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O12" s="13"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O12" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>51</v>
       </c>
@@ -2355,9 +2449,15 @@
       <c r="N13" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O13" s="13"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O13" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>51</v>
       </c>
@@ -2400,9 +2500,15 @@
       <c r="N14" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O14" s="13"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O14" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>51</v>
       </c>
@@ -2445,9 +2551,15 @@
       <c r="N15" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O15" s="13"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O15" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>51</v>
       </c>
@@ -2490,9 +2602,15 @@
       <c r="N16" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O16" s="13"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O16" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>51</v>
       </c>
@@ -2535,9 +2653,15 @@
       <c r="N17" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O17" s="13"/>
-    </row>
-    <row r="18" spans="1:15" ht="25" x14ac:dyDescent="0.35">
+      <c r="O17" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="13"/>
+    </row>
+    <row r="18" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2580,9 +2704,15 @@
       <c r="N18" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O18" s="13"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O18" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="13"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2625,28 +2755,36 @@
       <c r="N19" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O19" s="13"/>
-    </row>
-    <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
+      <c r="O19" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="13"/>
+    </row>
+    <row r="20" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>105</v>
       </c>
@@ -2689,9 +2827,15 @@
       <c r="N21" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O21" s="13"/>
-    </row>
-    <row r="22" spans="1:15" ht="25" x14ac:dyDescent="0.35">
+      <c r="O21" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q21" s="13"/>
+    </row>
+    <row r="22" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>105</v>
       </c>
@@ -2734,9 +2878,15 @@
       <c r="N22" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O22" s="13"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O22" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q22" s="13"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>105</v>
       </c>
@@ -2779,9 +2929,15 @@
       <c r="N23" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O23" s="13"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O23" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="13"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>105</v>
       </c>
@@ -2824,9 +2980,15 @@
       <c r="N24" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O24" s="13"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O24" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="13"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
         <v>105</v>
       </c>
@@ -2869,9 +3031,15 @@
       <c r="N25" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O25" s="13"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O25" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="13"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
         <v>105</v>
       </c>
@@ -2914,9 +3082,15 @@
       <c r="N26" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O26" s="13"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O26" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>105</v>
       </c>
@@ -2959,9 +3133,15 @@
       <c r="N27" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O27" s="13"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>105</v>
       </c>
@@ -3004,9 +3184,15 @@
       <c r="N28" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O28" s="13"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O28" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="13"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>105</v>
       </c>
@@ -3049,9 +3235,15 @@
       <c r="N29" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O29" s="13"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O29" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q29" s="13"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
         <v>105</v>
       </c>
@@ -3094,9 +3286,15 @@
       <c r="N30" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O30" s="13"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O30" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q30" s="13"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
         <v>105</v>
       </c>
@@ -3139,9 +3337,15 @@
       <c r="N31" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O31" s="13"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O31" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q31" s="13"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -3184,9 +3388,15 @@
       <c r="N32" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O32" s="13"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O32" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q32" s="13"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>105</v>
       </c>
@@ -3229,9 +3439,15 @@
       <c r="N33" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O33" s="13"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O33" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q33" s="13"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>105</v>
       </c>
@@ -3274,9 +3490,15 @@
       <c r="N34" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O34" s="13"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O34" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>105</v>
       </c>
@@ -3319,9 +3541,15 @@
       <c r="N35" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O35" s="13"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O35" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q35" s="13"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>105</v>
       </c>
@@ -3364,9 +3592,15 @@
       <c r="N36" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O36" s="13"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q36" s="13"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>105</v>
       </c>
@@ -3409,9 +3643,15 @@
       <c r="N37" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O37" s="13"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O37" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="13"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>105</v>
       </c>
@@ -3454,9 +3694,15 @@
       <c r="N38" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O38" s="13"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O38" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q38" s="13"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>105</v>
       </c>
@@ -3499,9 +3745,15 @@
       <c r="N39" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O39" s="13"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="13"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>105</v>
       </c>
@@ -3544,9 +3796,15 @@
       <c r="N40" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O40" s="13"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O40" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q40" s="13"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>105</v>
       </c>
@@ -3589,9 +3847,15 @@
       <c r="N41" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O41" s="13"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O41" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="13"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>105</v>
       </c>
@@ -3634,28 +3898,36 @@
       <c r="N42" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O42" s="13"/>
-    </row>
-    <row r="43" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="21" t="s">
+      <c r="O42" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q42" s="13"/>
+    </row>
+    <row r="43" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="12" t="s">
         <v>172</v>
       </c>
@@ -3698,9 +3970,15 @@
       <c r="N44" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O44" s="13"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O44" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P44" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q44" s="13"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="12" t="s">
         <v>172</v>
       </c>
@@ -3743,9 +4021,15 @@
       <c r="N45" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O45" s="13"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O45" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P45" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q45" s="13"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
         <v>172</v>
       </c>
@@ -3788,28 +4072,36 @@
       <c r="N46" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O46" s="13"/>
-    </row>
-    <row r="47" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="21" t="s">
+      <c r="O46" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P46" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q46" s="13"/>
+    </row>
+    <row r="47" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-    </row>
-    <row r="48" spans="1:15" ht="25" x14ac:dyDescent="0.35">
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
+      <c r="K47" s="23"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="23"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="23"/>
+      <c r="Q47" s="23"/>
+    </row>
+    <row r="48" spans="1:17" ht="25" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>181</v>
       </c>
@@ -3852,9 +4144,15 @@
       <c r="N48" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O48" s="13"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O48" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P48" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q48" s="13"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
         <v>181</v>
       </c>
@@ -3897,9 +4195,15 @@
       <c r="N49" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O49" s="13"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O49" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P49" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q49" s="13"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
         <v>181</v>
       </c>
@@ -3942,9 +4246,15 @@
       <c r="N50" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O50" s="13"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O50" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P50" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q50" s="13"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>181</v>
       </c>
@@ -3987,9 +4297,15 @@
       <c r="N51" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O51" s="13"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O51" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P51" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q51" s="13"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>181</v>
       </c>
@@ -4032,9 +4348,15 @@
       <c r="N52" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O52" s="13"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O52" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P52" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q52" s="13"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>181</v>
       </c>
@@ -4077,28 +4399,36 @@
       <c r="N53" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="O53" s="13"/>
-    </row>
-    <row r="54" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="O53" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P53" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q53" s="13"/>
+    </row>
+    <row r="54" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="22"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="23"/>
+      <c r="L54" s="23"/>
+      <c r="M54" s="23"/>
+      <c r="N54" s="23"/>
+      <c r="O54" s="23"/>
+      <c r="P54" s="23"/>
+      <c r="Q54" s="23"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="12" t="s">
         <v>199</v>
       </c>
@@ -4141,9 +4471,15 @@
       <c r="N55" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O55" s="13"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O55" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P55" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="13"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>199</v>
       </c>
@@ -4186,9 +4522,15 @@
       <c r="N56" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O56" s="13"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O56" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P56" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="13"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>199</v>
       </c>
@@ -4231,9 +4573,15 @@
       <c r="N57" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O57" s="13"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O57" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P57" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="13"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>199</v>
       </c>
@@ -4276,9 +4624,15 @@
       <c r="N58" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O58" s="13"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O58" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P58" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="13"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>199</v>
       </c>
@@ -4321,9 +4675,15 @@
       <c r="N59" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O59" s="13"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O59" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P59" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="13"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
         <v>199</v>
       </c>
@@ -4366,9 +4726,15 @@
       <c r="N60" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O60" s="13"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O60" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="13"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
         <v>199</v>
       </c>
@@ -4411,9 +4777,15 @@
       <c r="N61" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O61" s="13"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O61" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P61" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="13"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
         <v>199</v>
       </c>
@@ -4456,28 +4828,36 @@
       <c r="N62" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O62" s="13"/>
-    </row>
-    <row r="63" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="21" t="s">
+      <c r="O62" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P62" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="13"/>
+    </row>
+    <row r="63" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="23"/>
+      <c r="K63" s="23"/>
+      <c r="L63" s="23"/>
+      <c r="M63" s="23"/>
+      <c r="N63" s="23"/>
+      <c r="O63" s="23"/>
+      <c r="P63" s="23"/>
+      <c r="Q63" s="23"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
         <v>225</v>
       </c>
@@ -4520,9 +4900,15 @@
       <c r="N64" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O64" s="13"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O64" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P64" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q64" s="13"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
         <v>225</v>
       </c>
@@ -4565,9 +4951,15 @@
       <c r="N65" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O65" s="13"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O65" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P65" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q65" s="13"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
         <v>225</v>
       </c>
@@ -4610,9 +5002,15 @@
       <c r="N66" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="O66" s="13"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O66" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q66" s="13"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
         <v>225</v>
       </c>
@@ -4655,9 +5053,15 @@
       <c r="N67" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O67" s="13"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O67" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P67" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q67" s="13"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" s="12" t="s">
         <v>225</v>
       </c>
@@ -4700,18 +5104,24 @@
       <c r="N68" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="O68" s="13"/>
+      <c r="O68" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P68" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q68" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A63:O63"/>
-    <mergeCell ref="A47:O47"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A54:O54"/>
-    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A63:Q63"/>
+    <mergeCell ref="A47:Q47"/>
+    <mergeCell ref="A20:Q20"/>
+    <mergeCell ref="A54:Q54"/>
+    <mergeCell ref="A43:Q43"/>
   </mergeCells>
-  <conditionalFormatting sqref="F2:N68">
+  <conditionalFormatting sqref="F2:P68">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -4720,10 +5130,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:N68" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="F2:P68" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="O1" r:id="rId1" xr:uid="{7D43F78B-9D17-43E7-A092-A5DFAA3C7383}"/>
+    <hyperlink ref="P1" r:id="rId2" xr:uid="{EF261761-CA63-4066-A6B9-FA1F22D4ECA4}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4762,14 +5176,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -5112,14 +5526,14 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
     </row>
     <row r="21" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
@@ -5562,14 +5976,14 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
     </row>
     <row r="44" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
@@ -5632,14 +6046,14 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
     </row>
     <row r="48" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
@@ -5762,14 +6176,14 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
     </row>
     <row r="55" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
@@ -5932,14 +6346,14 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
     </row>
     <row r="64" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
@@ -6064,20 +6478,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
     </row>
     <row r="3" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="23"/>
     </row>
     <row r="4" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
@@ -6102,10 +6516,10 @@
       <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="23"/>
     </row>
     <row r="9" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
@@ -6128,10 +6542,10 @@
       <c r="B11" s="7"/>
     </row>
     <row r="12" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="B12" s="22"/>
+      <c r="B12" s="23"/>
     </row>
     <row r="13" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
@@ -6170,10 +6584,10 @@
       <c r="B17" s="7"/>
     </row>
     <row r="18" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="B18" s="22"/>
+      <c r="B18" s="23"/>
     </row>
     <row r="19" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
@@ -6216,8 +6630,8 @@
       <c r="B25" s="7"/>
     </row>
     <row r="26" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="23"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="23"/>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>

--- a/Users_Permissions.xlsx
+++ b/Users_Permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DominikDannenbauer\Documents\GitHub\project-dachau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EAEA61-4E69-4F5B-AB0D-A9B2D9339115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DE57BD-16E2-4B8B-B87A-BFF9E705F636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
